--- a/学生住宿情况表.xlsx
+++ b/学生住宿情况表.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserComputer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infomation-of-107\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$F$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="161">
   <si>
     <t>学生姓名</t>
   </si>
@@ -55,6 +55,9 @@
     <t>性别</t>
   </si>
   <si>
+    <t>家长联系电话</t>
+  </si>
+  <si>
     <t>白宇皓</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>男</t>
   </si>
   <si>
+    <t>15090218009</t>
+  </si>
+  <si>
     <t>曹瑞洋</t>
   </si>
   <si>
@@ -76,229 +82,439 @@
     <t>女</t>
   </si>
   <si>
+    <t>13598736538</t>
+  </si>
+  <si>
     <t>陈一诺</t>
   </si>
   <si>
+    <t>15539326958</t>
+  </si>
+  <si>
     <t>程佳欣</t>
   </si>
   <si>
     <t>走读无铺</t>
   </si>
   <si>
+    <t>15716350298</t>
+  </si>
+  <si>
+    <t>高灿</t>
+  </si>
+  <si>
     <t>崔佳乐</t>
   </si>
   <si>
+    <t>13525282268</t>
+  </si>
+  <si>
     <t>崔一尚</t>
   </si>
   <si>
+    <t>13513943021</t>
+  </si>
+  <si>
     <t>翟光辉</t>
   </si>
   <si>
+    <t>18238327212</t>
+  </si>
+  <si>
     <t>丁亦佳</t>
   </si>
   <si>
+    <t>13939363372</t>
+  </si>
+  <si>
     <t>杜晨阳</t>
   </si>
   <si>
+    <t>13839283759</t>
+  </si>
+  <si>
     <t>段宛辰</t>
   </si>
   <si>
     <t>范明信</t>
   </si>
   <si>
+    <t>15890496073</t>
+  </si>
+  <si>
     <t>房建设</t>
   </si>
   <si>
+    <t>13938339608</t>
+  </si>
+  <si>
     <t>冯梦乐</t>
   </si>
   <si>
+    <t>13193572112</t>
+  </si>
+  <si>
     <t>付泽熙</t>
   </si>
   <si>
-    <t>高灿</t>
+    <t>18239357168</t>
+  </si>
+  <si>
+    <t>15703933753</t>
   </si>
   <si>
     <t>高一品</t>
   </si>
   <si>
+    <t>18739381405</t>
+  </si>
+  <si>
     <t>关子豪</t>
   </si>
   <si>
+    <t>15839358163</t>
+  </si>
+  <si>
     <t>郭展孜</t>
   </si>
   <si>
+    <t>19639399998</t>
+  </si>
+  <si>
     <t>郝苗苗</t>
   </si>
   <si>
+    <t>13461702187</t>
+  </si>
+  <si>
     <t>胡心怡</t>
   </si>
   <si>
+    <t>15936754215</t>
+  </si>
+  <si>
     <t>胡钰涵</t>
   </si>
   <si>
+    <t>13525618067</t>
+  </si>
+  <si>
     <t>黄哲</t>
   </si>
   <si>
+    <t>18639352711</t>
+  </si>
+  <si>
     <t>李昂</t>
   </si>
   <si>
+    <t>18338048888</t>
+  </si>
+  <si>
     <t>李佳涵</t>
   </si>
   <si>
+    <t>13783934087</t>
+  </si>
+  <si>
     <t>李佳睿</t>
   </si>
   <si>
+    <t>18338020888</t>
+  </si>
+  <si>
     <t>李佳颖</t>
   </si>
   <si>
+    <t>18639389836</t>
+  </si>
+  <si>
+    <t>刘紫涵</t>
+  </si>
+  <si>
     <t>李静可</t>
   </si>
   <si>
+    <t>13653933521</t>
+  </si>
+  <si>
     <t>李凯旋</t>
   </si>
   <si>
+    <t>15936777061</t>
+  </si>
+  <si>
     <t>李名洋</t>
   </si>
   <si>
+    <t>15639306288</t>
+  </si>
+  <si>
     <t>李旭晨</t>
   </si>
   <si>
+    <t>13903935797</t>
+  </si>
+  <si>
     <t>李雅婷</t>
   </si>
   <si>
+    <t>15729279897</t>
+  </si>
+  <si>
     <t>李依柔</t>
   </si>
   <si>
+    <t>18568818855</t>
+  </si>
+  <si>
     <t>李泽瑞</t>
   </si>
   <si>
+    <t>13623932898</t>
+  </si>
+  <si>
     <t>刘浩宇</t>
   </si>
   <si>
+    <t>13939386005</t>
+  </si>
+  <si>
     <t>刘珈宁</t>
   </si>
   <si>
+    <t>18303932266</t>
+  </si>
+  <si>
     <t>刘家硕</t>
   </si>
   <si>
     <t>刘鹏</t>
   </si>
   <si>
+    <t>18639372028</t>
+  </si>
+  <si>
     <t>刘修阔</t>
   </si>
   <si>
+    <t>13523933662</t>
+  </si>
+  <si>
     <t>刘艺诺</t>
   </si>
   <si>
+    <t>13839351366</t>
+  </si>
+  <si>
     <t>刘宇腾</t>
   </si>
   <si>
-    <t>刘紫涵</t>
+    <t>18939343366</t>
+  </si>
+  <si>
+    <t>13949735762</t>
   </si>
   <si>
     <t>龙浩宇</t>
   </si>
   <si>
+    <t>13781379430</t>
+  </si>
+  <si>
     <t>马艺澄</t>
   </si>
   <si>
+    <t>13721712731</t>
+  </si>
+  <si>
     <t>孟伟旭</t>
   </si>
   <si>
+    <t>17339303182</t>
+  </si>
+  <si>
     <t>孟宪爽</t>
   </si>
   <si>
     <t>祁瀚辉</t>
   </si>
   <si>
+    <t>13781369836</t>
+  </si>
+  <si>
     <t>秦乙涵</t>
   </si>
   <si>
+    <t>15839336710</t>
+  </si>
+  <si>
     <t>史宋涵</t>
   </si>
   <si>
+    <t>13938309563</t>
+  </si>
+  <si>
     <t>宋佳怡</t>
   </si>
   <si>
+    <t>18039355500</t>
+  </si>
+  <si>
     <t>宋世豪</t>
   </si>
   <si>
+    <t>13839279109</t>
+  </si>
+  <si>
     <t>苏韵之</t>
   </si>
   <si>
+    <t>18239371983</t>
+  </si>
+  <si>
     <t>苏子煊</t>
   </si>
   <si>
+    <t>13673021779</t>
+  </si>
+  <si>
     <t>孙晨歌</t>
   </si>
   <si>
+    <t>15939323292</t>
+  </si>
+  <si>
     <t>田啸童</t>
   </si>
   <si>
+    <t>13781357190</t>
+  </si>
+  <si>
     <t>汪士航</t>
   </si>
   <si>
+    <t>15539339658</t>
+  </si>
+  <si>
     <t>王光辉</t>
   </si>
   <si>
+    <t>15039382562</t>
+  </si>
+  <si>
     <t>王潇怡</t>
   </si>
   <si>
+    <t>13461656277</t>
+  </si>
+  <si>
     <t>王梓航</t>
   </si>
   <si>
+    <t>15210263209</t>
+  </si>
+  <si>
     <t>王梓豪</t>
   </si>
   <si>
+    <t>18300650709</t>
+  </si>
+  <si>
     <t>王梓怡</t>
   </si>
   <si>
+    <t>13803936210</t>
+  </si>
+  <si>
     <t>吴浩然</t>
   </si>
   <si>
+    <t>15939318302</t>
+  </si>
+  <si>
     <t>吴延旭</t>
   </si>
   <si>
+    <t>15936786198</t>
+  </si>
+  <si>
     <t>谢佳欣</t>
   </si>
   <si>
+    <t>15824857522</t>
+  </si>
+  <si>
     <t>许敬涛</t>
   </si>
   <si>
+    <t>15518522809</t>
+  </si>
+  <si>
     <t>许钊迪</t>
   </si>
   <si>
+    <t>17339325202</t>
+  </si>
+  <si>
     <t>杨亚静</t>
   </si>
   <si>
+    <t>13461709630</t>
+  </si>
+  <si>
     <t>杨雨露</t>
   </si>
   <si>
-    <t>姚丁恺</t>
+    <t>13939392757</t>
   </si>
   <si>
     <t>于夕露</t>
   </si>
   <si>
+    <t>13721799805</t>
+  </si>
+  <si>
     <t>张静雪</t>
   </si>
   <si>
+    <t>18639341832</t>
+  </si>
+  <si>
     <t>张梦朵</t>
   </si>
   <si>
+    <t>13603839494</t>
+  </si>
+  <si>
     <t>张献雷</t>
   </si>
   <si>
+    <t>15518512212</t>
+  </si>
+  <si>
     <t>张游龙</t>
   </si>
   <si>
+    <t>13461623165</t>
+  </si>
+  <si>
     <t>张跃虎</t>
   </si>
   <si>
+    <t>13643938925</t>
+  </si>
+  <si>
     <t>赵辰逸</t>
   </si>
   <si>
+    <t>18539330756</t>
+  </si>
+  <si>
     <t>赵腾源</t>
+  </si>
+  <si>
+    <t>13613932000</t>
   </si>
   <si>
     <t>左晓阳</t>
@@ -314,7 +530,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +550,24 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="13"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -345,6 +579,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -826,137 +1067,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -969,19 +1210,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1036,7 +1295,17 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1240,25 +1509,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1518,13 +1787,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O78"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="4" width="9" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.625" customWidth="1"/>
+    <col min="8" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1547,1517 +1817,1803 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:15">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="15" hidden="1" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="O2" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" ht="15" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:15">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:15">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" ht="15" hidden="1" spans="1:15">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:15">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="15" hidden="1" spans="1:15">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="1" spans="1:15">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" ht="15" spans="1:15">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:15">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="15" hidden="1" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:15">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" ht="15" hidden="1" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:15">
-      <c r="A11" s="5" t="s">
-        <v>21</v>
+      <c r="A11" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:15">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8">
+        <v>13903937336</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" ht="15" hidden="1" spans="1:15">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:15">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="15" hidden="1" spans="1:15">
+      <c r="A13" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="15" hidden="1" spans="1:15">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" ht="15" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="15" hidden="1" spans="1:15">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" ht="15" spans="1:15">
-      <c r="A15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:15">
       <c r="A16" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" ht="15" hidden="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="15" hidden="1" spans="1:8">
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:8">
+      <c r="A19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" ht="15" spans="1:8">
+      <c r="A21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" ht="15" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" ht="15" spans="1:8">
+      <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" ht="15" hidden="1" spans="1:8">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" ht="15" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:6">
-      <c r="A20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:6">
-      <c r="A21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:8">
+      <c r="A24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" ht="15" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" ht="15" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" ht="15" hidden="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" ht="15" hidden="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" ht="15" hidden="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" ht="15" hidden="1" spans="1:8">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" ht="15" spans="1:6">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" ht="15" hidden="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" ht="15" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" ht="15" hidden="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" ht="15" hidden="1" spans="1:8">
+      <c r="A35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" ht="15" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" ht="15" hidden="1" spans="1:8">
+      <c r="A36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" ht="15" spans="1:6">
-      <c r="A36" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>8</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" ht="15" hidden="1" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="14">
+        <v>13839281869</v>
+      </c>
+    </row>
+    <row r="38" ht="15" hidden="1" spans="1:8">
+      <c r="A38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" ht="15" spans="1:6">
-      <c r="A38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>8</v>
-      </c>
       <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" ht="15" hidden="1" spans="1:8">
+      <c r="A39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" ht="15" spans="1:6">
-      <c r="A39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:8">
+      <c r="A40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" ht="15" hidden="1" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" ht="15" hidden="1" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" ht="15" spans="1:6">
-      <c r="A40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:6">
-      <c r="A41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:6">
-      <c r="A42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:6">
-      <c r="A43" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" ht="15" hidden="1" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" ht="15" hidden="1" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:6">
-      <c r="A46" s="8" t="s">
-        <v>56</v>
+        <v>10</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" ht="15" hidden="1" spans="1:8">
+      <c r="A46" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="14">
+        <v>13939312589</v>
+      </c>
+    </row>
+    <row r="47" ht="15" hidden="1" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" ht="15" spans="1:6">
-      <c r="A47" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="48" ht="15" spans="1:6">
-      <c r="A48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" ht="15" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" ht="15" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" ht="15" hidden="1" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="52" ht="15" spans="1:6">
-      <c r="A52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" ht="15" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" ht="15" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" ht="15" hidden="1" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" ht="15" hidden="1" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" ht="15" hidden="1" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="56" ht="15" spans="1:6">
-      <c r="A56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="F58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" ht="15" hidden="1" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" ht="15" hidden="1" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="57" ht="15" spans="1:6">
-      <c r="A57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" ht="15" spans="1:6">
-      <c r="A58" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" ht="15" spans="1:6">
-      <c r="A59" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" ht="15" spans="1:6">
-      <c r="A60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" ht="15" hidden="1" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" ht="15" hidden="1" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" ht="15" hidden="1" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="63" ht="15" spans="1:6">
-      <c r="A63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" ht="15" hidden="1" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" ht="15" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" ht="15" hidden="1" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" ht="15" hidden="1" spans="1:8">
+      <c r="A66" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" ht="15" spans="1:8">
+      <c r="A68" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" ht="15" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="66" ht="15" spans="1:6">
-      <c r="A66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="F69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" ht="15" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" ht="15" spans="1:8">
+      <c r="A71" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="67" ht="15" spans="1:6">
-      <c r="A67" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" ht="15" spans="1:6">
-      <c r="A68" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" ht="15" spans="1:6">
-      <c r="A69" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" ht="15" spans="1:6">
-      <c r="A70" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" ht="15" spans="1:6">
-      <c r="A71" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" ht="15" spans="1:6">
-      <c r="A72" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" ht="15" hidden="1" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" ht="15" hidden="1" spans="1:8">
       <c r="A73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C73" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" ht="15" hidden="1" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" ht="15" hidden="1" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" ht="15" hidden="1" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="74" ht="15" spans="1:6">
-      <c r="A74" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" ht="15" spans="1:6">
-      <c r="A75" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" ht="15" spans="1:6">
-      <c r="A76" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" ht="15" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" ht="15" hidden="1" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" ht="15" spans="1:6">
-      <c r="A78" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G77" s="4">
+        <v>13721726762</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="E1:F78" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="E1:F77" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="走读留铺"/>
+        <filter val="住宿"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="女"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
-  <sortState ref="A2:C78">
+  <sortState ref="A2:G77">
     <sortCondition ref="A2"/>
   </sortState>
-  <conditionalFormatting sqref="A2:A78">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="H53">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H67">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A77">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2 G6:G8 G10 G12:G15 G17:G18 G23 G26 G29:G31 G34:G39 G41 G43 G45:G47 G51 G55:G57 G59:G60 G62:G63 G65:G66 G72:G77">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H67 A3:A71">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H5 H9 H11 H16 H19:H22 H24:H25 H27:H28 H32:H33 H40 H42 H44 H48:H50 H52 H54 H58 H61 H64">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/学生住宿情况表.xlsx
+++ b/学生住宿情况表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="160">
   <si>
     <t>学生姓名</t>
   </si>
@@ -85,6 +85,12 @@
     <t>13598736538</t>
   </si>
   <si>
+    <t>陈聚隆</t>
+  </si>
+  <si>
+    <t>走读无铺</t>
+  </si>
+  <si>
     <t>陈一诺</t>
   </si>
   <si>
@@ -94,72 +100,69 @@
     <t>程佳欣</t>
   </si>
   <si>
-    <t>走读无铺</t>
-  </si>
-  <si>
     <t>15716350298</t>
   </si>
   <si>
+    <t>崔家乐</t>
+  </si>
+  <si>
+    <t>13525282268</t>
+  </si>
+  <si>
+    <t>崔一尚</t>
+  </si>
+  <si>
+    <t>13513943021</t>
+  </si>
+  <si>
+    <t>翟光辉</t>
+  </si>
+  <si>
+    <t>18238327212</t>
+  </si>
+  <si>
+    <t>丁亦佳</t>
+  </si>
+  <si>
+    <t>13939363372</t>
+  </si>
+  <si>
+    <t>杜晨阳</t>
+  </si>
+  <si>
+    <t>13839283759</t>
+  </si>
+  <si>
+    <t>段宛辰</t>
+  </si>
+  <si>
+    <t>范明信</t>
+  </si>
+  <si>
+    <t>15890496073</t>
+  </si>
+  <si>
+    <t>房建设</t>
+  </si>
+  <si>
+    <t>13938339608</t>
+  </si>
+  <si>
+    <t>冯梦乐</t>
+  </si>
+  <si>
+    <t>13193572112</t>
+  </si>
+  <si>
+    <t>付泽熙</t>
+  </si>
+  <si>
+    <t>18239357168</t>
+  </si>
+  <si>
     <t>高灿</t>
   </si>
   <si>
-    <t>崔佳乐</t>
-  </si>
-  <si>
-    <t>13525282268</t>
-  </si>
-  <si>
-    <t>崔一尚</t>
-  </si>
-  <si>
-    <t>13513943021</t>
-  </si>
-  <si>
-    <t>翟光辉</t>
-  </si>
-  <si>
-    <t>18238327212</t>
-  </si>
-  <si>
-    <t>丁亦佳</t>
-  </si>
-  <si>
-    <t>13939363372</t>
-  </si>
-  <si>
-    <t>杜晨阳</t>
-  </si>
-  <si>
-    <t>13839283759</t>
-  </si>
-  <si>
-    <t>段宛辰</t>
-  </si>
-  <si>
-    <t>范明信</t>
-  </si>
-  <si>
-    <t>15890496073</t>
-  </si>
-  <si>
-    <t>房建设</t>
-  </si>
-  <si>
-    <t>13938339608</t>
-  </si>
-  <si>
-    <t>冯梦乐</t>
-  </si>
-  <si>
-    <t>13193572112</t>
-  </si>
-  <si>
-    <t>付泽熙</t>
-  </si>
-  <si>
-    <t>18239357168</t>
-  </si>
-  <si>
     <t>15703933753</t>
   </si>
   <si>
@@ -205,12 +208,6 @@
     <t>18639352711</t>
   </si>
   <si>
-    <t>李昂</t>
-  </si>
-  <si>
-    <t>18338048888</t>
-  </si>
-  <si>
     <t>李佳涵</t>
   </si>
   <si>
@@ -229,88 +226,88 @@
     <t>18639389836</t>
   </si>
   <si>
+    <t>李静可</t>
+  </si>
+  <si>
+    <t>13653933521</t>
+  </si>
+  <si>
+    <t>李凯旋</t>
+  </si>
+  <si>
+    <t>15936777061</t>
+  </si>
+  <si>
+    <t>李名洋</t>
+  </si>
+  <si>
+    <t>15639306288</t>
+  </si>
+  <si>
+    <t>李旭晨</t>
+  </si>
+  <si>
+    <t>13903935797</t>
+  </si>
+  <si>
+    <t>李雅婷</t>
+  </si>
+  <si>
+    <t>15729279897</t>
+  </si>
+  <si>
+    <t>李依柔</t>
+  </si>
+  <si>
+    <t>18568818855</t>
+  </si>
+  <si>
+    <t>李泽瑞</t>
+  </si>
+  <si>
+    <t>13623932898</t>
+  </si>
+  <si>
+    <t>刘浩宇</t>
+  </si>
+  <si>
+    <t>13939386005</t>
+  </si>
+  <si>
+    <t>刘珈宁</t>
+  </si>
+  <si>
+    <t>18303932266</t>
+  </si>
+  <si>
+    <t>刘家硕</t>
+  </si>
+  <si>
+    <t>刘鹏</t>
+  </si>
+  <si>
+    <t>18639372028</t>
+  </si>
+  <si>
+    <t>刘修阔</t>
+  </si>
+  <si>
+    <t>13523933662</t>
+  </si>
+  <si>
+    <t>刘艺诺</t>
+  </si>
+  <si>
+    <t>13839351366</t>
+  </si>
+  <si>
+    <t>刘宇腾</t>
+  </si>
+  <si>
+    <t>18939343366</t>
+  </si>
+  <si>
     <t>刘紫涵</t>
-  </si>
-  <si>
-    <t>李静可</t>
-  </si>
-  <si>
-    <t>13653933521</t>
-  </si>
-  <si>
-    <t>李凯旋</t>
-  </si>
-  <si>
-    <t>15936777061</t>
-  </si>
-  <si>
-    <t>李名洋</t>
-  </si>
-  <si>
-    <t>15639306288</t>
-  </si>
-  <si>
-    <t>李旭晨</t>
-  </si>
-  <si>
-    <t>13903935797</t>
-  </si>
-  <si>
-    <t>李雅婷</t>
-  </si>
-  <si>
-    <t>15729279897</t>
-  </si>
-  <si>
-    <t>李依柔</t>
-  </si>
-  <si>
-    <t>18568818855</t>
-  </si>
-  <si>
-    <t>李泽瑞</t>
-  </si>
-  <si>
-    <t>13623932898</t>
-  </si>
-  <si>
-    <t>刘浩宇</t>
-  </si>
-  <si>
-    <t>13939386005</t>
-  </si>
-  <si>
-    <t>刘珈宁</t>
-  </si>
-  <si>
-    <t>18303932266</t>
-  </si>
-  <si>
-    <t>刘家硕</t>
-  </si>
-  <si>
-    <t>刘鹏</t>
-  </si>
-  <si>
-    <t>18639372028</t>
-  </si>
-  <si>
-    <t>刘修阔</t>
-  </si>
-  <si>
-    <t>13523933662</t>
-  </si>
-  <si>
-    <t>刘艺诺</t>
-  </si>
-  <si>
-    <t>13839351366</t>
-  </si>
-  <si>
-    <t>刘宇腾</t>
-  </si>
-  <si>
-    <t>18939343366</t>
   </si>
   <si>
     <t>13949735762</t>
@@ -555,10 +552,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1197,18 +1195,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1216,26 +1214,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1295,17 +1284,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1509,25 +1488,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1787,18 +1766,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O77"/>
+  <sheetPr/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="4" width="9" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="7" max="7" width="12.625" customWidth="1"/>
     <col min="8" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:15">
+    <row r="1" ht="15" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,11 +1796,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15" hidden="1" spans="1:15">
+    <row r="2" ht="15" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1843,9 +1822,8 @@
       <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" ht="15" spans="1:15">
+    </row>
+    <row r="3" ht="15" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1867,9 +1845,10 @@
       <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" ht="15" spans="1:15">
-      <c r="A4" s="3" t="s">
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" ht="18.75" spans="1:14">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1878,21 +1857,18 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" ht="15" hidden="1" spans="1:15">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>18238389229</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1902,141 +1878,139 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:14">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="15" hidden="1" spans="1:15">
-      <c r="A6" s="3" t="s">
+    <row r="7" ht="15" spans="1:14">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="15" hidden="1" spans="1:15">
-      <c r="A7" s="3" t="s">
+    <row r="8" ht="15" customHeight="1" spans="1:14">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="15" hidden="1" spans="1:15">
-      <c r="A8" s="3" t="s">
+    <row r="9" ht="15" spans="1:14">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:15">
-      <c r="A9" s="3" t="s">
+    <row r="10" ht="15" spans="1:14">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" ht="15" hidden="1" spans="1:15">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="11" ht="15" spans="1:14">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:15">
-      <c r="A11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2047,20 +2021,17 @@
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8">
-        <v>13903937336</v>
-      </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" ht="15" hidden="1" spans="1:15">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:14">
       <c r="A12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -2071,40 +2042,40 @@
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="7">
+        <v>13903937336</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="15" hidden="1" spans="1:15">
-      <c r="A13" s="9" t="s">
+    <row r="14" ht="15" spans="1:14">
+      <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" ht="15" hidden="1" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
@@ -2118,12 +2089,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" ht="15" hidden="1" spans="1:15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:14">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
@@ -2141,36 +2112,35 @@
         <v>10</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:14">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="1:15">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="4" t="s">
+    <row r="17" ht="15" spans="1:7">
+      <c r="A17" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" ht="15" hidden="1" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -2185,15 +2155,15 @@
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:7">
+      <c r="A18" s="3" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="18" ht="15" hidden="1" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -2211,12 +2181,12 @@
         <v>10</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:7">
+      <c r="A19" s="3" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -2231,16 +2201,15 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:7">
+      <c r="A20" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -2258,14 +2227,13 @@
         <v>14</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:7">
+      <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -2276,20 +2244,19 @@
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:7">
+      <c r="A22" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
@@ -2300,42 +2267,41 @@
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:7">
+      <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" ht="15" hidden="1" spans="1:8">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="4" t="s">
+    </row>
+    <row r="24" ht="15" spans="1:7">
+      <c r="A24" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -2350,16 +2316,15 @@
         <v>9</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:7">
+      <c r="A25" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -2377,13 +2342,12 @@
         <v>14</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:7">
+      <c r="A26" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" ht="15" hidden="1" spans="1:8">
-      <c r="A26" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -2401,12 +2365,12 @@
         <v>10</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:7">
+      <c r="A27" s="3" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="27" ht="15" hidden="1" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -2416,21 +2380,18 @@
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:7">
+      <c r="A28" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -2448,13 +2409,12 @@
         <v>14</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" ht="15" hidden="1" spans="1:8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:7">
       <c r="A29" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -2472,12 +2432,12 @@
         <v>10</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" ht="15" hidden="1" spans="1:8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:7">
       <c r="A30" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -2495,12 +2455,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" ht="15" hidden="1" spans="1:8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:7">
       <c r="A31" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -2516,12 +2476,12 @@
         <v>10</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:7">
       <c r="A32" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
@@ -2537,13 +2497,12 @@
         <v>14</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" ht="15" spans="1:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:7">
       <c r="A33" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -2561,36 +2520,35 @@
         <v>14</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" ht="15" hidden="1" spans="1:8">
-      <c r="A34" s="3" t="s">
+    </row>
+    <row r="35" ht="15" spans="1:7">
+      <c r="A35" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" ht="15" hidden="1" spans="1:8">
-      <c r="A35" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -2608,35 +2566,35 @@
         <v>10</v>
       </c>
       <c r="G35" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" ht="15" hidden="1" spans="1:8">
-      <c r="A36" s="3" t="s">
+    <row r="37" ht="15" spans="1:7">
+      <c r="A37" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" ht="15" hidden="1" spans="1:8">
-      <c r="A37" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -2651,36 +2609,36 @@
       <c r="F37" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="11">
         <v>13839281869</v>
       </c>
     </row>
-    <row r="38" ht="15" hidden="1" spans="1:8">
+    <row r="38" ht="15" spans="1:7">
       <c r="A38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:7">
+      <c r="A39" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" ht="15" hidden="1" spans="1:8">
-      <c r="A39" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -2698,12 +2656,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:7">
       <c r="A40" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -2721,13 +2679,12 @@
         <v>14</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" ht="15" hidden="1" spans="1:8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:7">
       <c r="A41" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -2745,12 +2702,12 @@
         <v>10</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -2768,13 +2725,12 @@
         <v>14</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:7">
+      <c r="A43" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" ht="15" hidden="1" spans="1:8">
-      <c r="A43" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -2792,12 +2748,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:7">
+      <c r="A44" s="2" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="44" ht="15" hidden="1" spans="1:8">
-      <c r="A44" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -2805,21 +2761,18 @@
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:7">
+      <c r="A45" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" ht="15" hidden="1" spans="1:8">
-      <c r="A45" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>8</v>
@@ -2837,12 +2790,12 @@
         <v>10</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:7">
+      <c r="A46" s="10" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="46" ht="15" hidden="1" spans="1:8">
-      <c r="A46" s="13" t="s">
-        <v>99</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -2857,13 +2810,13 @@
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="11">
         <v>13939312589</v>
       </c>
     </row>
-    <row r="47" ht="15" hidden="1" spans="1:8">
+    <row r="47" ht="15" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>8</v>
@@ -2881,12 +2834,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:7">
+      <c r="A48" s="2" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="48" ht="15" spans="1:8">
-      <c r="A48" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>8</v>
@@ -2904,13 +2857,12 @@
         <v>14</v>
       </c>
       <c r="G48" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:7">
+      <c r="A49" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" ht="15" spans="1:8">
-      <c r="A49" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>8</v>
@@ -2928,13 +2880,12 @@
         <v>14</v>
       </c>
       <c r="G49" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="1:7">
+      <c r="A50" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" ht="15" spans="1:8">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
@@ -2950,13 +2901,12 @@
         <v>14</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="1:7">
+      <c r="A51" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" ht="15" hidden="1" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
@@ -2974,12 +2924,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:7">
+      <c r="A52" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="52" ht="15" spans="1:8">
-      <c r="A52" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>8</v>
@@ -2997,13 +2947,12 @@
         <v>14</v>
       </c>
       <c r="G52" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="1:7">
+      <c r="A53" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" ht="15" spans="1:8">
-      <c r="A53" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>8</v>
@@ -3021,13 +2970,12 @@
         <v>14</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="1:7">
+      <c r="A54" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" ht="15" spans="1:8">
-      <c r="A54" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>8</v>
@@ -3045,13 +2993,12 @@
         <v>14</v>
       </c>
       <c r="G54" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:7">
+      <c r="A55" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" ht="15" hidden="1" spans="1:8">
-      <c r="A55" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>8</v>
@@ -3069,12 +3016,12 @@
         <v>10</v>
       </c>
       <c r="G55" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="1:7">
+      <c r="A56" s="2" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="56" ht="15" hidden="1" spans="1:8">
-      <c r="A56" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>8</v>
@@ -3092,12 +3039,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" ht="15" spans="1:7">
+      <c r="A57" s="2" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="57" ht="15" hidden="1" spans="1:8">
-      <c r="A57" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>8</v>
@@ -3115,12 +3062,12 @@
         <v>10</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:7">
+      <c r="A58" s="2" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="58" ht="15" spans="1:8">
-      <c r="A58" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>8</v>
@@ -3138,13 +3085,12 @@
         <v>14</v>
       </c>
       <c r="G58" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:7">
+      <c r="A59" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="H58" s="12"/>
-    </row>
-    <row r="59" ht="15" hidden="1" spans="1:8">
-      <c r="A59" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>8</v>
@@ -3162,12 +3108,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" ht="15" spans="1:7">
+      <c r="A60" s="2" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="60" ht="15" hidden="1" spans="1:8">
-      <c r="A60" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>8</v>
@@ -3185,12 +3131,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" ht="15" spans="1:7">
+      <c r="A61" s="2" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="61" ht="15" hidden="1" spans="1:8">
-      <c r="A61" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>8</v>
@@ -3200,19 +3146,18 @@
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:7">
+      <c r="A62" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" ht="15" hidden="1" spans="1:8">
-      <c r="A62" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>8</v>
@@ -3230,12 +3175,12 @@
         <v>10</v>
       </c>
       <c r="G62" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" ht="15" spans="1:7">
+      <c r="A63" s="2" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="63" ht="15" hidden="1" spans="1:8">
-      <c r="A63" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>8</v>
@@ -3253,12 +3198,12 @@
         <v>10</v>
       </c>
       <c r="G63" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:7">
+      <c r="A64" s="2" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="64" ht="15" hidden="1" spans="1:8">
-      <c r="A64" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>8</v>
@@ -3268,21 +3213,18 @@
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" ht="15" spans="1:7">
+      <c r="A65" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="65" ht="15" hidden="1" spans="1:8">
-      <c r="A65" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>8</v>
@@ -3300,12 +3242,12 @@
         <v>10</v>
       </c>
       <c r="G65" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" ht="15" spans="1:7">
+      <c r="A66" s="2" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="66" ht="15" hidden="1" spans="1:8">
-      <c r="A66" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>8</v>
@@ -3323,12 +3265,12 @@
         <v>10</v>
       </c>
       <c r="G66" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:7">
+      <c r="A67" s="2" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="67" ht="15" spans="1:8">
-      <c r="A67" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>8</v>
@@ -3346,13 +3288,12 @@
         <v>14</v>
       </c>
       <c r="G67" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" ht="15" spans="1:7">
+      <c r="A68" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="H67" s="12"/>
-    </row>
-    <row r="68" ht="15" spans="1:8">
-      <c r="A68" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>8</v>
@@ -3370,12 +3311,12 @@
         <v>14</v>
       </c>
       <c r="G68" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" ht="15" spans="1:7">
+      <c r="A69" s="2" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="69" ht="15" spans="1:8">
-      <c r="A69" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>8</v>
@@ -3393,12 +3334,12 @@
         <v>14</v>
       </c>
       <c r="G69" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" ht="15" spans="1:7">
+      <c r="A70" s="2" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="70" ht="15" spans="1:8">
-      <c r="A70" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>8</v>
@@ -3416,12 +3357,12 @@
         <v>14</v>
       </c>
       <c r="G70" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" ht="15" spans="1:7">
+      <c r="A71" s="10" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="71" ht="15" spans="1:8">
-      <c r="A71" s="13" t="s">
-        <v>148</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>8</v>
@@ -3439,12 +3380,12 @@
         <v>14</v>
       </c>
       <c r="G71" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" ht="15" spans="1:7">
+      <c r="A72" s="2" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="72" ht="15" hidden="1" spans="1:8">
-      <c r="A72" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
@@ -3460,12 +3401,12 @@
         <v>10</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" ht="15" spans="1:7">
+      <c r="A73" s="2" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="73" ht="15" hidden="1" spans="1:8">
-      <c r="A73" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>8</v>
@@ -3483,12 +3424,12 @@
         <v>10</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" ht="15" spans="1:7">
+      <c r="A74" s="2" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="74" ht="15" hidden="1" spans="1:8">
-      <c r="A74" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
@@ -3502,12 +3443,12 @@
         <v>10</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" ht="15" spans="1:7">
+      <c r="A75" s="2" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="75" ht="15" hidden="1" spans="1:8">
-      <c r="A75" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>8</v>
@@ -3525,12 +3466,12 @@
         <v>10</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" ht="15" spans="1:7">
+      <c r="A76" s="2" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="76" ht="15" hidden="1" spans="1:8">
-      <c r="A76" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>8</v>
@@ -3548,12 +3489,12 @@
         <v>10</v>
       </c>
       <c r="G76" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" ht="15" spans="1:7">
+      <c r="A77" s="2" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="77" ht="15" hidden="1" spans="1:8">
-      <c r="A77" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>8</v>
@@ -3576,44 +3517,21 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="E1:F77" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="走读留铺"/>
-        <filter val="住宿"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="女"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
-  <sortState ref="A2:G77">
+  <sortState ref="A2:G78">
     <sortCondition ref="A2"/>
   </sortState>
-  <conditionalFormatting sqref="H53">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H67">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A77">
+  <conditionalFormatting sqref="A3:A77">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2 G6:G8 G10 G12:G15 G17:G18 G23 G26 G29:G31 G34:G39 G41 G43 G45:G47 G51 G55:G57 G59:G60 G62:G63 G65:G66 G72:G77">
+  <conditionalFormatting sqref="A4:A71">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3 G7:G9 G11 G13:G16 G18:G19 G24 G26 G29:G31 G34:G39 G41 G43 G45:G47 G51 G55:G57 G59:G60 G62:G63 G65:G66 G72:G77">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H67 A3:A71">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5 H9 H11 H16 H19:H22 H24:H25 H27:H28 H32:H33 H40 H42 H44 H48:H50 H52 H54 H58 H61 H64">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/学生住宿情况表.xlsx
+++ b/学生住宿情况表.xlsx
@@ -1777,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:O79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1841,7 +1841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="15" hidden="1" spans="1:15">
+    <row r="3" ht="15" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" ht="15" hidden="1" spans="1:15">
+    <row r="4" ht="15" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="15" hidden="1" spans="1:15">
+    <row r="5" ht="15" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15" hidden="1" spans="1:15">
+    <row r="9" ht="15" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" ht="15" hidden="1" spans="1:15">
+    <row r="11" ht="15" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="15" hidden="1" spans="1:15">
+    <row r="16" ht="15" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" ht="15" hidden="1" spans="1:8">
+    <row r="19" ht="15" spans="1:8">
       <c r="A19" s="3" t="s">
         <v>47</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="15" hidden="1" spans="1:8">
+    <row r="20" ht="15" spans="1:8">
       <c r="A20" s="3" t="s">
         <v>49</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" ht="15" hidden="1" spans="1:8">
+    <row r="21" ht="15" spans="1:8">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" ht="15" hidden="1" spans="1:8">
+    <row r="22" ht="15" spans="1:8">
       <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" ht="15" hidden="1" spans="1:8">
+    <row r="24" ht="15" spans="1:8">
       <c r="A24" s="3" t="s">
         <v>57</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" ht="15" hidden="1" spans="1:8">
+    <row r="26" ht="15" spans="1:8">
       <c r="A26" s="3" t="s">
         <v>61</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" ht="15" hidden="1" spans="1:8">
+    <row r="27" ht="15" spans="1:8">
       <c r="A27" s="3" t="s">
         <v>63</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" ht="15" hidden="1" spans="1:8">
+    <row r="31" ht="15" spans="1:8">
       <c r="A31" s="3" t="s">
         <v>71</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" ht="15" hidden="1" spans="1:8">
+    <row r="32" ht="15" spans="1:8">
       <c r="A32" s="3" t="s">
         <v>73</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" ht="15" hidden="1" spans="1:8">
+    <row r="39" ht="15" spans="1:8">
       <c r="A39" s="2" t="s">
         <v>86</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="41" ht="15" hidden="1" spans="1:8">
+    <row r="41" ht="15" spans="1:8">
       <c r="A41" s="2" t="s">
         <v>90</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" ht="15" hidden="1" spans="1:8">
+    <row r="43" ht="15" spans="1:8">
       <c r="A43" s="2" t="s">
         <v>94</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" ht="15" hidden="1" spans="1:8">
+    <row r="47" ht="15" spans="1:8">
       <c r="A47" s="2" t="s">
         <v>101</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" ht="15" hidden="1" spans="1:8">
+    <row r="48" ht="15" spans="1:8">
       <c r="A48" s="2" t="s">
         <v>103</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" ht="15" hidden="1" spans="1:8">
+    <row r="49" ht="15" spans="1:8">
       <c r="A49" s="2" t="s">
         <v>105</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" ht="15" hidden="1" spans="1:8">
+    <row r="51" ht="15" spans="1:8">
       <c r="A51" s="2" t="s">
         <v>109</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" ht="15" hidden="1" spans="1:8">
+    <row r="52" ht="15" spans="1:8">
       <c r="A52" s="2" t="s">
         <v>111</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" ht="15" hidden="1" spans="1:8">
+    <row r="53" ht="15" spans="1:8">
       <c r="A53" s="2" t="s">
         <v>113</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" ht="15" hidden="1" spans="1:8">
+    <row r="57" ht="15" spans="1:8">
       <c r="A57" s="2" t="s">
         <v>121</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="60" ht="15" hidden="1" spans="1:8">
+    <row r="60" ht="15" spans="1:8">
       <c r="A60" s="2" t="s">
         <v>127</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="63" ht="15" hidden="1" spans="1:8">
+    <row r="63" ht="15" spans="1:8">
       <c r="A63" s="2" t="s">
         <v>133</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" ht="15" hidden="1" spans="1:8">
+    <row r="66" ht="15" spans="1:8">
       <c r="A66" s="2" t="s">
         <v>139</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="67" ht="15" hidden="1" spans="1:8">
+    <row r="67" ht="15" spans="1:8">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" ht="15" hidden="1" spans="1:8">
+    <row r="68" ht="15" spans="1:8">
       <c r="A68" s="2" t="s">
         <v>143</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="69" ht="15" hidden="1" spans="1:8">
+    <row r="69" ht="15" spans="1:8">
       <c r="A69" s="2" t="s">
         <v>145</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" ht="15" hidden="1" spans="1:8">
+    <row r="70" ht="15" spans="1:8">
       <c r="A70" s="10" t="s">
         <v>147</v>
       </c>
@@ -3762,11 +3762,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="F1:G77" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="男"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <sortState ref="A2:H78">
